--- a/inst/templates/soils_data_entry.xlsx
+++ b/inst/templates/soils_data_entry.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
+  <si>
+    <t xml:space="preserve">SOILS FIELD DATA FORM  ·  Alberta Wetland Assessment</t>
+  </si>
   <si>
     <t xml:space="preserve">project_id</t>
   </si>
@@ -28,52 +31,31 @@
     <t xml:space="preserve">observer</t>
   </si>
   <si>
+    <t xml:space="preserve">method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">depth_restrict_cm</t>
+  </si>
+  <si>
     <t xml:space="preserve">date</t>
   </si>
   <si>
-    <t xml:space="preserve">gps_e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gps_n</t>
-  </si>
-  <si>
-    <t xml:space="preserve">datum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">waypoint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">water_table_cm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">series</t>
-  </si>
-  <si>
-    <t xml:space="preserve">subgroup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parent_material</t>
-  </si>
-  <si>
-    <t xml:space="preserve">slope_pct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">slope_position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">aspect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">surface_stones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drainage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">surface_expression</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comments</t>
+    <t xml:space="preserve">gps_easting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gps_northing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hydric_ind_present</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hydric_criterion_met</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soil_great_group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">additional_notes</t>
   </si>
   <si>
     <t xml:space="preserve">AB-2024-01</t>
@@ -88,6 +70,12 @@
     <t xml:space="preserve">J. Smith</t>
   </si>
   <si>
+    <t xml:space="preserve">Pit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85</t>
+  </si>
+  <si>
     <t xml:space="preserve">2024-06-15</t>
   </si>
   <si>
@@ -97,160 +85,97 @@
     <t xml:space="preserve">5900000</t>
   </si>
   <si>
-    <t xml:space="preserve">NAD83</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WP-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loon River</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orthic Humic Gleysol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GL</t>
+    <t xml:space="preserve">Yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Humic Gleysol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strong sulphidic odour; saturated at surface.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOILS FIELD DATA FORM  ·  Horizon Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">horizon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">depth_top_cm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">depth_bot_cm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">munsell_hue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">munsell_val</t>
+  </si>
+  <si>
+    <t xml:space="preserve">munsell_chr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">texture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">structure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">von_post</t>
+  </si>
+  <si>
+    <t xml:space="preserve">material</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mottles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">redox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10YR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
   </si>
   <si>
     <t xml:space="preserve">2</t>
   </si>
   <si>
-    <t xml:space="preserve">L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">l</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saturated at surface; strong sulphidic odour.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">layer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">horizon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">depth_top_cm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">depth_bot_cm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">color_hue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">color_value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">color_chroma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mottle_abundance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mottle_size</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mottle_contrast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">texture</t>
-  </si>
-  <si>
-    <t xml:space="preserve">structure_kind</t>
-  </si>
-  <si>
-    <t xml:space="preserve">structure_class</t>
-  </si>
-  <si>
-    <t xml:space="preserve">structure_grade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">consistence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cf_pct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cf_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">organics_comp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">organics_fib_cl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ph</t>
-  </si>
-  <si>
-    <t xml:space="preserve">notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ah</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10YR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">few</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">faint</t>
-  </si>
-  <si>
     <t xml:space="preserve">SiCL</t>
   </si>
   <si>
-    <t xml:space="preserve">AB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FR</t>
+    <t xml:space="preserve">SBK</t>
   </si>
   <si>
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">6.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strong redoximorphic features; oxidized root channels.</t>
+    <t xml:space="preserve">Min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Few</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oxidized root channels; abrupt smooth lower boundary.</t>
   </si>
   <si>
     <t xml:space="preserve">OVERVIEW</t>
   </si>
   <si>
-    <t xml:space="preserve">One row in 'plots' per field form; one row per soil horizon in 'horizons'. Delete the grey example rows before submitting. Sheet names must not be renamed — 01_ingest.Rmd reads them by name. plot_id must match exactly between the two sheets.</t>
+    <t xml:space="preserve">One row in 'plots' per field form (one plot per row). One row per soil horizon in 'horizons'. Delete the grey example rows before submitting. Sheet names must not be renamed — 01_ingest.Rmd reads them by name. plot_id must match exactly between the two sheets.</t>
   </si>
   <si>
     <t xml:space="preserve">DATE FORMAT</t>
@@ -259,40 +184,46 @@
     <t xml:space="preserve">Enter dates as YYYY-MM-DD text (e.g. 2024-06-15). Do not use Excel date serial numbers.</t>
   </si>
   <si>
-    <t xml:space="preserve">plots — columns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">project_id: project code | site_id: wetland site identifier | plot_id: primary key (must match horizons sheet) | water_table_cm: depth to water table in cm from surface (0 = at surface) | series: soil series name if known | subgroup: CSSC subgroup (e.g. Orthic Humic Gleysol) — classify after field season | parent_material: PM code (e.g. GL=glaciolacustrine, GT=glacial till, FL=fluvial, CO=colluvial) | slope_position: C=Crest, U=Upper, M=Middle, L=Lower, D=Depression, Level | surface_stones: S0 (none) to S5 (&gt;50% surface covered) | drainage: R=Rapid, W=Well, MW=Moderately Well, I=Imperfect, P=Poor, VP=Very Poor | surface_expression: CSSC surface expression codes (a=level, l=depression, etc.)</t>
+    <t xml:space="preserve">plots — header fields</t>
+  </si>
+  <si>
+    <t xml:space="preserve">project_id / site_id / plot_id: identifiers (plot_id is primary key) | method: Pit (soil pit excavated) or Probe (soil probe only) | depth_restrict_cm: depth in cm to restrictive layer (bedrock, dense till, etc.) | gps_easting / gps_northing: UTM Zone 11N or 12N, NAD83</t>
+  </si>
+  <si>
+    <t xml:space="preserve">plots — footer fields</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hydric_ind_present: Yes / No — were any hydric soil indicators observed? | hydric_criterion_met: Yes / No / Marginal — overall hydric soil determination | soil_great_group: CSSC great group from field assessment (e.g. Humic Gleysol, Mesisol, Luvic Gleysol) — classify after field season if uncertain | additional_notes: free-text notes from the form footer</t>
   </si>
   <si>
     <t xml:space="preserve">horizons — Munsell colour</t>
   </si>
   <si>
-    <t xml:space="preserve">Record moist Munsell colour in three separate columns: color_hue (e.g. 10YR, 2.5Y, 5GY, GLEY1), color_value (numeric, 0-10), color_chroma (numeric, 0-8). For gleyed colours use Gley chart notation in hue (e.g. GLEY1 5/10GY). Leave all three blank if colour not recorded for that horizon.</t>
+    <t xml:space="preserve">Record moist Munsell colour in three columns: munsell_hue (e.g. 10YR, 2.5Y, 5GY, GLEY1), munsell_val (numeric 0-10), munsell_chr (numeric 0-8). Gleyed colours: use Gley chart hue notation (e.g. GLEY1).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">horizons — texture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Select one texture class matching the field form checkboxes: S=Sand, LS=Loamy Sand, SL=Sandy Loam, L=Loam, SiL=Silt Loam, Si=Silt, SCL=Sandy Clay Loam, CL=Clay Loam, SiCL=Silty Clay Loam, SC=Sandy Clay, SiC=Silty Clay, C=Clay, Muck, Peat.</t>
   </si>
   <si>
     <t xml:space="preserve">horizons — structure</t>
   </si>
   <si>
-    <t xml:space="preserve">structure_kind: M=massive, PL=platy, PR=prismatic, CO=columnar, AB=angular blocky, SB=subangular blocky, GR=granular, CR=crumb, SG=single grain. | structure_class: VF=very fine, F=fine, M=medium, C=coarse, VC=very coarse. | structure_grade: 0=structureless, 1=weak, 2=moderate, 3=strong. Leave blank for structureless (massive/single grain) horizons.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">horizons — consistence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moist consistence: L=loose, VFR=very friable, FR=friable, FI=firm, VFI=very firm, EFI=extremely firm.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">horizons — organics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">organics_comp: dominant organic component (e.g. Sphagnum, Sedge, Reed, Wood, Mixed). organics_fib_cl: CSSC organic fibre class — Fi=Fibric (Von Post H1-H3; &gt;40% unrubbed fibre), Me=Mesic (H4-H6; 17-40% unrubbed fibre), Hu=Humic (H7-H10; &lt;17% unrubbed fibre). Only complete for O and Of/Om/Oh horizon designations.</t>
+    <t xml:space="preserve">Select one structure code matching the field form checkboxes: GR=Granular, PL=Platy, BK=Angular Blocky, SBK=Subangular Blocky, PR=Prismatic, MA=Massive.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">horizons — Von Post</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Von Post humification scale H1–H10 for organic horizons. H1-H3 = Fibric (&gt;40% fibre, raw peat); H4-H6 = Mesic (17-40% fibre, moderately decomposed); H7-H10 = Humic (&lt;17% fibre, well decomposed). Leave blank for mineral horizons.</t>
   </si>
   <si>
     <t xml:space="preserve">DO NOT COMPUTE</t>
   </si>
   <si>
-    <t xml:space="preserve">The following are computed by R from the horizons table and reference tables — do NOT enter them here: von_post (Von Post humification score from organics_fib_cl), hydric_indicators (derived from colour, mottles, horizon sequence), peat_depth_cm (sum of organic horizon thicknesses), cssc_great_group (classified in 03_transform.Rmd from horizon sequence).</t>
+    <t xml:space="preserve">The following are derived by R in 03_transform.Rmd — do NOT enter manually: peat_depth_cm (sum of Peat/Muck horizon thicknesses), organic_fibre_class (from von_post: Fi/Me/Hu), hydric_indicators list (from colour, mottles, redox, horizon sequence), cssc_great_group_confirmed (CSSC classification from horizon sequence).</t>
   </si>
 </sst>
 </file>
@@ -300,13 +231,19 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <b/>
     </font>
     <font>
       <sz val="8"/>
@@ -332,12 +269,17 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E5090"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -381,16 +323,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -681,7 +626,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
-    <tabColor rgb="FF5C3A1E"/>
+    <tabColor rgb="FF2E5090"/>
   </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
@@ -690,192 +635,147 @@
     <col min="2" max="2" width="12.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="16.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="12.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="8.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="12.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="12.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="9.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="10.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="11.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="16.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="26.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="12.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="8.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="11.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="8.71" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="10.71" hidden="0" customWidth="1"/>
-    <col min="18" max="18" width="10.71" hidden="0" customWidth="1"/>
-    <col min="19" max="19" width="11.71" hidden="0" customWidth="1"/>
-    <col min="20" max="20" width="40.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="13.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="13.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="13.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="13.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="24.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="44.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="38" customHeight="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+    </row>
+    <row r="2" ht="38" customHeight="1">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="K2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="L2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="M2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="E3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="F3" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="J3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="K3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="M3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>39</v>
-      </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J1001">
+  <mergeCells count="1">
+    <mergeCell ref="A1:M1"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:F1003">
       <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N1001">
-      <formula1>0</formula1>
-      <formula2>100</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>"NAD83,WGS84"</xm:f>
+            <xm:f>"Pit,Probe"</xm:f>
           </x14:formula1>
-          <xm:sqref>H2:H1001</xm:sqref>
+          <xm:sqref>E4:E1003</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>"C,U,M,L,D,Level"</xm:f>
+            <xm:f>"Yes,No"</xm:f>
           </x14:formula1>
-          <xm:sqref>O2:O1001</xm:sqref>
+          <xm:sqref>J4:J1003</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>"S0,S1,S2,S3,S4,S5"</xm:f>
+            <xm:f>"Yes,No,Marginal"</xm:f>
           </x14:formula1>
-          <xm:sqref>Q2:Q1001</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"R,W,MW,I,P,VP"</xm:f>
-          </x14:formula1>
-          <xm:sqref>R2:R1001</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"a,b,f,h,i,l,m,r,s,t,u,v"</xm:f>
-          </x14:formula1>
-          <xm:sqref>S2:S1001</xm:sqref>
+          <xm:sqref>K4:K1003</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -886,199 +786,157 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
-    <tabColor rgb="FF8B5E3C"/>
+    <tabColor rgb="FF5C3A1E"/>
   </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="14.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="12.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="7.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="9.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="9.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="9.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="9.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="8.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="8.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="10.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="9.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="10.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="9.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="8.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="10.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="7.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="7.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="9.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="9.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="8.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="9.71" hidden="0" customWidth="1"/>
     <col min="13" max="13" width="9.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="10.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="10.71" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="10.71" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="10.71" hidden="0" customWidth="1"/>
-    <col min="18" max="18" width="7.71" hidden="0" customWidth="1"/>
-    <col min="19" max="19" width="10.71" hidden="0" customWidth="1"/>
-    <col min="20" max="20" width="14.71" hidden="0" customWidth="1"/>
-    <col min="21" max="21" width="10.71" hidden="0" customWidth="1"/>
-    <col min="22" max="22" width="7.71" hidden="0" customWidth="1"/>
-    <col min="23" max="23" width="40.71" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="9.71" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="44.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="38" customHeight="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>26</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+    </row>
+    <row r="2" ht="38" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>69</v>
+        <v>36</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="V2" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="W2" s="2" t="s">
-        <v>76</v>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="6">
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1001">
+  <mergeCells count="1">
+    <mergeCell ref="A1:O1"/>
+  </mergeCells>
+  <dataValidations count="4">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D1003">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F1001">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E1003">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R1001">
-      <formula1>0</formula1>
-      <formula2>100</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V1001">
-      <formula1>0</formula1>
-      <formula2>14</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H1001">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G1003">
       <formula1>0</formula1>
       <formula2>10</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I1001">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H4:H1003">
       <formula1>0</formula1>
       <formula2>8</formula2>
     </dataValidation>
@@ -1087,66 +945,42 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="10">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>"none,few,common,many"</xm:f>
+            <xm:f>"S,LS,SL,L,SiL,Si,SCL,CL,SiCL,SC,SiC,C,Muck,Peat"</xm:f>
           </x14:formula1>
-          <xm:sqref>J2:J1001</xm:sqref>
+          <xm:sqref>I4:I1003</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>"fine,medium,coarse"</xm:f>
+            <xm:f>"GR,PL,BK,SBK,PR,MA"</xm:f>
           </x14:formula1>
-          <xm:sqref>K2:K1001</xm:sqref>
+          <xm:sqref>J4:J1003</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>"faint,distinct,prominent"</xm:f>
+            <xm:f>"H1,H2,H3,H4,H5,H6,H7,H8,H9,H10"</xm:f>
           </x14:formula1>
-          <xm:sqref>L2:L1001</xm:sqref>
+          <xm:sqref>K4:K1003</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>"O,S,LS,SL,FSL,VFSL,L,SiL,Si,SCL,CL,SiCL,SC,SiC,C"</xm:f>
+            <xm:f>"Min,Peat,Muck,Marl"</xm:f>
           </x14:formula1>
-          <xm:sqref>M2:M1001</xm:sqref>
+          <xm:sqref>L4:L1003</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>"M,PL,PR,CO,AB,SB,GR,CR,SG"</xm:f>
+            <xm:f>"None,Few,Com,Many"</xm:f>
           </x14:formula1>
-          <xm:sqref>N2:N1001</xm:sqref>
+          <xm:sqref>M4:M1003</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>"VF,F,M,C,VC"</xm:f>
+            <xm:f>"None,Few,Com,Many"</xm:f>
           </x14:formula1>
-          <xm:sqref>O2:O1001</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"0,1,2,3"</xm:f>
-          </x14:formula1>
-          <xm:sqref>P2:P1001</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"L,VFR,FR,FI,VFI,EFI"</xm:f>
-          </x14:formula1>
-          <xm:sqref>Q2:Q1001</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"gravel,cobble,stone,boulder,flagstone,channer"</xm:f>
-          </x14:formula1>
-          <xm:sqref>S2:S1001</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>"Fi,Me,Hu"</xm:f>
-          </x14:formula1>
-          <xm:sqref>U2:U1001</xm:sqref>
+          <xm:sqref>N4:N1003</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1166,68 +1000,76 @@
     <col min="2" max="2" width="85.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>78</v>
+    <row r="1" ht="44" customHeight="1">
+      <c r="A1" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" ht="90" customHeight="1">
-      <c r="A3" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>82</v>
+      <c r="A2" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="4" ht="72" customHeight="1">
-      <c r="A4" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="5" ht="72" customHeight="1">
-      <c r="A5" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="7" ht="72" customHeight="1">
-      <c r="A7" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>90</v>
+      <c r="A4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" ht="72" customHeight="1">
+      <c r="A6" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="8" ht="72" customHeight="1">
-      <c r="A8" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>92</v>
+      <c r="A8" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" ht="72" customHeight="1">
+      <c r="A9" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/inst/templates/soils_data_entry.xlsx
+++ b/inst/templates/soils_data_entry.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
   <si>
     <t xml:space="preserve">SOILS FIELD DATA FORM  ·  Alberta Wetland Assessment</t>
   </si>
@@ -46,6 +46,21 @@
     <t xml:space="preserve">gps_northing</t>
   </si>
   <si>
+    <t xml:space="preserve">slope_position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">slope_pct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aspect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drainage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">surface_stones</t>
+  </si>
+  <si>
     <t xml:space="preserve">hydric_ind_present</t>
   </si>
   <si>
@@ -85,6 +100,21 @@
     <t xml:space="preserve">5900000</t>
   </si>
   <si>
+    <t xml:space="preserve">L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S0</t>
+  </si>
+  <si>
     <t xml:space="preserve">Yes</t>
   </si>
   <si>
@@ -127,10 +157,13 @@
     <t xml:space="preserve">material</t>
   </si>
   <si>
-    <t xml:space="preserve">mottles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">redox</t>
+    <t xml:space="preserve">mottle_abundance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mottle_size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mottle_contrast</t>
   </si>
   <si>
     <t xml:space="preserve">notes</t>
@@ -151,9 +184,6 @@
     <t xml:space="preserve">3</t>
   </si>
   <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
     <t xml:space="preserve">SiCL</t>
   </si>
   <si>
@@ -169,6 +199,12 @@
     <t xml:space="preserve">Few</t>
   </si>
   <si>
+    <t xml:space="preserve">Fine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distinct</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oxidized root channels; abrupt smooth lower boundary.</t>
   </si>
   <si>
@@ -196,6 +232,18 @@
     <t xml:space="preserve">hydric_ind_present: Yes / No — were any hydric soil indicators observed? | hydric_criterion_met: Yes / No / Marginal — overall hydric soil determination | soil_great_group: CSSC great group from field assessment (e.g. Humic Gleysol, Mesisol, Luvic Gleysol) — classify after field season if uncertain | additional_notes: free-text notes from the form footer</t>
   </si>
   <si>
+    <t xml:space="preserve">plots — physiography</t>
+  </si>
+  <si>
+    <t xml:space="preserve">slope_position: C=crest / U=upper / M=mid / L=lower / D=depression / Level | slope_pct: slope gradient in percent (0 = level; may exceed 100 on steep slopes) | aspect: downslope compass direction — N / NE / E / SE / S / SW / W / NW, or Flat where there is no aspect | drainage (CSSC 7-class): VR=very rapidly / R=rapidly / W=well / MW=moderately well / I=imperfectly / P=poorly / VP=very poorly drained | surface_stones: CSSC surface stoniness class S0 (nonstony) through S5 (exceedingly stony)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">horizons — horizon code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">horizon: choose from the dropdown of standard CSSC horizon designations (organic L / F / H / LFH / O / Of / Om / Oh; A horizons Ah / Ahe / Ahg / Ae / Aeg / Ap / AB; B horizons Bm / Bg / Bgf / Bf / Bfg / Bh / Bhf / Bt / Btg / Btjg / Bnt / Bss; C horizons C / Cg / Ck / Ckg / Cca / Css; R; W). Letters only — the protocol does not use numbered subdivisions. The list is drawn from data-raw/cssc_great_groups.csv plus common wetland horizons; if a horizon you need is missing, add it to the dropdown in create_soils_template.R.</t>
+  </si>
+  <si>
     <t xml:space="preserve">horizons — Munsell colour</t>
   </si>
   <si>
@@ -220,10 +268,16 @@
     <t xml:space="preserve">Von Post humification scale H1–H10 for organic horizons. H1-H3 = Fibric (&gt;40% fibre, raw peat); H4-H6 = Mesic (17-40% fibre, moderately decomposed); H7-H10 = Humic (&lt;17% fibre, well decomposed). Leave blank for mineral horizons.</t>
   </si>
   <si>
+    <t xml:space="preserve">horizons — mottles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Record mottles / redoximorphic features in three separate columns, matching the field-form checkbox groups: mottle_abundance: None / Few / Common / Many (form codes None / Few / Com / Many) | mottle_size: Fine / Medium / Coarse (form codes F / M / C) | mottle_contrast: Faint / Distinct / Prominent (form codes F / D / P). Set mottle_abundance to None (or leave the row blank) when no mottles are present; leave mottle_size and mottle_contrast blank in that case.</t>
+  </si>
+  <si>
     <t xml:space="preserve">DO NOT COMPUTE</t>
   </si>
   <si>
-    <t xml:space="preserve">The following are derived by R in 03_transform.Rmd — do NOT enter manually: peat_depth_cm (sum of Peat/Muck horizon thicknesses), organic_fibre_class (from von_post: Fi/Me/Hu), hydric_indicators list (from colour, mottles, redox, horizon sequence), cssc_great_group_confirmed (CSSC classification from horizon sequence).</t>
+    <t xml:space="preserve">The following are derived by R in 03_transform.Rmd — do NOT enter manually: peat_depth_cm (sum of Peat/Muck horizon thicknesses), organic_fibre_class (from von_post: Fi/Me/Hu), hydric_indicators list (from colour, mottle characteristics, horizon sequence), cssc_great_group_confirmed (CSSC classification from horizon sequence).</t>
   </si>
 </sst>
 </file>
@@ -641,9 +695,14 @@
     <col min="8" max="8" width="13.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="13.71" hidden="0" customWidth="1"/>
     <col min="10" max="10" width="13.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="13.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="24.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="44.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="9.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="9.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="9.71" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="13.71" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="13.71" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="13.71" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="24.71" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="44.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -662,6 +721,11 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
     </row>
     <row r="2" ht="38" customHeight="1">
       <c r="A2" s="2" t="s">
@@ -703,54 +767,87 @@
       <c r="M2" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="N2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>25</v>
+        <v>31</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A1:R1"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:F1003">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4:K1003">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -758,7 +855,7 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="7">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"Pit,Probe"</xm:f>
@@ -769,13 +866,37 @@
           <x14:formula1>
             <xm:f>"Yes,No"</xm:f>
           </x14:formula1>
+          <xm:sqref>O4:O1003</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"Yes,No,Marginal"</xm:f>
+          </x14:formula1>
+          <xm:sqref>P4:P1003</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"C,U,M,L,D,Level"</xm:f>
+          </x14:formula1>
           <xm:sqref>J4:J1003</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>"Yes,No,Marginal"</xm:f>
-          </x14:formula1>
-          <xm:sqref>K4:K1003</xm:sqref>
+            <xm:f>"N,NE,E,SE,S,SW,W,NW,Flat"</xm:f>
+          </x14:formula1>
+          <xm:sqref>L4:L1003</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"VR,R,W,MW,I,P,VP"</xm:f>
+          </x14:formula1>
+          <xm:sqref>M4:M1003</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"S0,S1,S2,S3,S4,S5"</xm:f>
+          </x14:formula1>
+          <xm:sqref>N4:N1003</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -803,14 +924,15 @@
     <col min="10" max="10" width="9.71" hidden="0" customWidth="1"/>
     <col min="11" max="11" width="8.71" hidden="0" customWidth="1"/>
     <col min="12" max="12" width="9.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="9.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="9.71" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="44.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="11.71" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="10.71" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="11.71" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="44.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -826,6 +948,7 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
     </row>
     <row r="2" ht="38" customHeight="1">
       <c r="A2" s="2" t="s">
@@ -835,95 +958,101 @@
         <v>3</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>39</v>
+        <v>49</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A1:P1"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D1003">
@@ -945,7 +1074,13 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="8">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"L,F,H,LFH,O,Of,Om,Oh,Ah,Ahe,Ahg,Ae,Aeg,Ap,AB,Bm,Bg,Bgf,Bf,Bfg,Bh,Bhf,Bt,Btg,Btjg,Bnt,Bss,C,Cg,Ck,Ckg,Cca,Css,R,W"</xm:f>
+          </x14:formula1>
+          <xm:sqref>C4:C1003</xm:sqref>
+        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"S,LS,SL,L,SiL,Si,SCL,CL,SiCL,SC,SiC,C,Muck,Peat"</xm:f>
@@ -972,15 +1107,21 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>"None,Few,Com,Many"</xm:f>
+            <xm:f>"None,Few,Common,Many"</xm:f>
           </x14:formula1>
           <xm:sqref>M4:M1003</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>"None,Few,Com,Many"</xm:f>
+            <xm:f>"Fine,Medium,Coarse"</xm:f>
           </x14:formula1>
           <xm:sqref>N4:N1003</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"Faint,Distinct,Prominent"</xm:f>
+          </x14:formula1>
+          <xm:sqref>O4:O1003</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1002,74 +1143,98 @@
   <sheetData>
     <row r="1" ht="44" customHeight="1">
       <c r="A1" s="4" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" ht="60" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" ht="72" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" ht="72" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" ht="72" customHeight="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" ht="96" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" ht="72" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="9" ht="72" customHeight="1">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>69</v>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10" ht="72" customHeight="1">
+      <c r="A10" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" ht="72" customHeight="1">
+      <c r="A11" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="12" ht="72" customHeight="1">
+      <c r="A12" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
